--- a/Employee_Reports_wi52/Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage Q0568.xlsx
+++ b/Employee_Reports_wi52/Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage Q0568.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1710,20 +1710,20 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>320</v>
+        <v>727</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1756,11 +1756,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7905</v>
+        <v>7897</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
